--- a/backend/test_codes/table_analyzer_codes/outputs2/e30214c2-bb28-4650-8ef0-43c2c27cc0b5_039_final.xlsx
+++ b/backend/test_codes/table_analyzer_codes/outputs2/e30214c2-bb28-4650-8ef0-43c2c27cc0b5_039_final.xlsx
@@ -425,20 +425,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="4" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="5" customWidth="1" min="8" max="8"/>
     <col width="5" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -519,17 +519,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;10</t>
+          <t>10&gt;&gt;其他项目</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>a&gt;&gt;2024年第四季度&gt;&gt;折算前数值</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -539,17 +539,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年第四季度</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>-人民币百万元百分比除外</t>
         </is>
       </c>
     </row>
@@ -574,12 +574,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;10</t>
+          <t>10&gt;&gt;其他项目</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>b&gt;&gt;2024年第四季度&gt;&gt;折算后数值</t>
+          <t>a&gt;&gt;2024年第四季度&gt;&gt;折算前数值</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
     </row>
@@ -629,12 +629,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;11</t>
+          <t>10&gt;&gt;其他项目</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>a&gt;&gt;2024年第四季度&gt;&gt;折算前数值</t>
+          <t>b&gt;&gt;2024年第四季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2166218</t>
+          <t>b</t>
         </is>
       </c>
     </row>
@@ -684,17 +684,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;11</t>
+          <t>11&gt;&gt;其中:与衍生工具及其他抵(质)押品要求相关的现金流出</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>b&gt;&gt;2024年第四季度&gt;&gt;折算后数值</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -704,17 +704,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年第四季度</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>278418</t>
+          <t>其他项目</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;12</t>
+          <t>11&gt;&gt;其中:与衍生工具及其他抵(质)押品要求相关的现金流出</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>75603</t>
+          <t>2166218</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;12</t>
+          <t>11&gt;&gt;其中:与衍生工具及其他抵(质)押品要求相关的现金流出</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>75603</t>
+          <t>278418</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;13</t>
+          <t>12&gt;&gt;其中:与抵(质)押债务工具融资流失相关的现金流出</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>a&gt;&gt;2024年第四季度&gt;&gt;折算前数值</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -869,17 +869,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年第四季度</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>其中:与衍生工具及其他抵(质)押品要求相关的现金流出</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;13</t>
+          <t>12&gt;&gt;其中:与抵(质)押债务工具融资流失相关的现金流出</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>b&gt;&gt;2024年第四季度&gt;&gt;折算后数值</t>
+          <t>a&gt;&gt;2024年第四季度&gt;&gt;折算前数值</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>75603</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;14</t>
+          <t>12&gt;&gt;其中:与抵(质)押债务工具融资流失相关的现金流出</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>a&gt;&gt;2024年第四季度&gt;&gt;折算前数值</t>
+          <t>b&gt;&gt;2024年第四季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2083482</t>
+          <t>75603</t>
         </is>
       </c>
     </row>
@@ -1014,17 +1014,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;14</t>
+          <t>13&gt;&gt;其中:信用便利和流动性便利</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>b&gt;&gt;2024年第四季度&gt;&gt;折算后数值</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1034,17 +1034,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年第四季度</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>195682</t>
+          <t>其中:与抵(质)押债务工具融资流失相关的现金流出</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;15</t>
+          <t>13&gt;&gt;其中:信用便利和流动性便利</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>7133</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;15</t>
+          <t>13&gt;&gt;其中:信用便利和流动性便利</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>7133</t>
         </is>
       </c>
     </row>
@@ -1179,17 +1179,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;16</t>
+          <t>14&gt;&gt;其他契约性融资义务</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>a&gt;&gt;2024年第四季度&gt;&gt;折算前数值</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年第四季度</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>6033921</t>
+          <t>其中:信用便利和流动性便利</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;16</t>
+          <t>14&gt;&gt;其他契约性融资义务</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>b&gt;&gt;2024年第四季度&gt;&gt;折算后数值</t>
+          <t>a&gt;&gt;2024年第四季度&gt;&gt;折算前数值</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>725.646</t>
+          <t>2083482</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>现金流入&gt;&gt;序号&gt;&gt;17</t>
+          <t>14&gt;&gt;其他契约性融资义务</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>7516892</t>
+          <t>195682</t>
         </is>
       </c>
     </row>
@@ -1344,17 +1344,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>现金流入&gt;&gt;序号&gt;&gt;19</t>
+          <t>15&gt;&gt;或有融资义务</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>a&gt;&gt;2024年第四季度&gt;&gt;折算前数值</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年第四季度</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>1062976</t>
+          <t>其他契约性融资义务</t>
         </is>
       </c>
     </row>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>现金流入&gt;&gt;序号&gt;&gt;19</t>
+          <t>15&gt;&gt;或有融资义务</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>b&gt;&gt;2024年第四季度&gt;&gt;折算后数值</t>
+          <t>a&gt;&gt;2024年第四季度&gt;&gt;折算前数值</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1062.976</t>
+          <t>5239</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>现金流入&gt;&gt;序号&gt;&gt;20</t>
+          <t>15&gt;&gt;或有融资义务</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>a&gt;&gt;2024年第四季度&gt;&gt;折算前数值</t>
+          <t>b&gt;&gt;2024年第四季度&gt;&gt;折算后数值</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.432106</t>
+          <t>5220</t>
         </is>
       </c>
     </row>
@@ -1509,17 +1509,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>现金流入&gt;&gt;序号&gt;&gt;20</t>
+          <t>16&gt;&gt;预期现金流出总量</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>b&gt;&gt;2024年第四季度&gt;&gt;折算后数值</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1529,17 +1529,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年第四季度</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.420346</t>
+          <t>或有融资义务</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;21</t>
+          <t>16&gt;&gt;预期现金流出总量</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>80.804</t>
+          <t>6033921</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;21</t>
+          <t>16&gt;&gt;预期现金流出总量</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>75.837</t>
+          <t>725.646</t>
         </is>
       </c>
     </row>
@@ -1674,17 +1674,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;22</t>
+          <t>现金流入&gt;&gt;17&gt;&gt;抵(质)押借贷(包括逆回购和借入证券)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>a&gt;&gt;2024年第四季度&gt;&gt;折算前数值</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1694,17 +1694,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年第四季度</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>3575886</t>
+          <t>预期现金流出总量</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;22</t>
+          <t>现金流入&gt;&gt;17&gt;&gt;抵(质)押借贷(包括逆回购和借入证券)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2559159</t>
+          <t>7516892</t>
         </is>
       </c>
     </row>
@@ -1784,17 +1784,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;23</t>
+          <t>现金流入&gt;&gt;19&gt;&gt;其他现金流入</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>b&gt;&gt;2024年第四季度&gt;&gt;折算后数值</t>
+          <t>(人民币百万元,百分比除外)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>发生额</t>
+          <t>占比</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1804,17 +1804,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>百万元</t>
+          <t>%</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2024年</t>
+          <t>2024年第四季度</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>6237408</t>
+          <t>抵(质)押借贷(包括逆回购和借入证券)</t>
         </is>
       </c>
     </row>
@@ -1839,12 +1839,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;22&gt;&gt;现金净流出量</t>
+          <t>现金流入&gt;&gt;19&gt;&gt;其他现金流入</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>b&gt;&gt;2024年第四季度&gt;&gt;折算后数值</t>
+          <t>a&gt;&gt;2024年第四季度&gt;&gt;折算前数值</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>4957733</t>
+          <t>1062976</t>
         </is>
       </c>
     </row>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>序号&gt;&gt;23&gt;&gt;流动性覆盖率(%)1</t>
+          <t>现金流入&gt;&gt;19&gt;&gt;其他现金流入</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1914,15 +1914,840 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>百万元</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1062.976</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>流动性覆盖率相关数据</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>现金流入&gt;&gt;20&gt;&gt;预期现金流入总量</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>(人民币百万元,百分比除外)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
           <t>%</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2024年第四季度</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>完全正常履约付款带来的现金流入</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>流动性覆盖率相关数据</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>现金流入&gt;&gt;20&gt;&gt;预期现金流入总量</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>a&gt;&gt;2024年第四季度&gt;&gt;折算前数值</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>百万元</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>2024年</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2.432106</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>流动性覆盖率相关数据</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>现金流入&gt;&gt;20&gt;&gt;预期现金流入总量</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>b&gt;&gt;2024年第四季度&gt;&gt;折算后数值</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>百万元</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>1.420346</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>流动性覆盖率相关数据</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>21&gt;&gt;合格优质流动性资产</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>(人民币百万元,百分比除外)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2024年第四季度</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>其他现金流入</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>流动性覆盖率相关数据</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>21&gt;&gt;合格优质流动性资产</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>a&gt;&gt;2024年第四季度&gt;&gt;折算前数值</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>百万元</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>80.804</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>流动性覆盖率相关数据</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>21&gt;&gt;合格优质流动性资产</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>b&gt;&gt;2024年第四季度&gt;&gt;折算后数值</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>百万元</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>75.837</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>流动性覆盖率相关数据</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>22&gt;&gt;现金净流出量</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>(人民币百万元,百分比除外)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2024年第四季度</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>预期现金流入总量</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>流动性覆盖率相关数据</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>22&gt;&gt;现金净流出量</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>a&gt;&gt;2024年第四季度&gt;&gt;折算前数值</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>百万元</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>3575886</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>流动性覆盖率相关数据</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>22&gt;&gt;现金净流出量</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>b&gt;&gt;2024年第四季度&gt;&gt;折算后数值</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>百万元</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2559159</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>流动性覆盖率相关数据</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>23&gt;&gt;流动性覆盖率(%)1</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>(人民币百万元,百分比除外)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2024年第四季度</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>合格优质流动性资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>流动性覆盖率相关数据</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>23&gt;&gt;流动性覆盖率(%)1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>b&gt;&gt;2024年第四季度&gt;&gt;折算后数值</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>6237408</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>流动性覆盖率相关数据</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>22&gt;&gt;现金净流出量</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>(人民币百万元,百分比除外)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2024年第四季度</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>现金净流出量</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>流动性覆盖率相关数据</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>22&gt;&gt;现金净流出量</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>b&gt;&gt;2024年第四季度&gt;&gt;折算后数值</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>百万元</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>4957733</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>流动性覆盖率相关数据</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>23&gt;&gt;流动性覆盖率(%)1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>(人民币百万元,百分比除外)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2024年第四季度</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>流动性覆盖率(%)1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>中国建设银行</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>流动性覆盖率相关数据</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>本集团</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>23&gt;&gt;流动性覆盖率(%)1</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>b&gt;&gt;2024年第四季度&gt;&gt;折算后数值</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>发生额</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>人民币</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>125.73</t>
         </is>
